--- a/data/global_sku_mapping.xlsx
+++ b/data/global_sku_mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Weavers Villa\Documents\GitHub\weavers-stock\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3F289D-9688-4750-AF0F-5C175EC10D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7111ADC2-8844-4F80-AEA5-3D0B7DCAA126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27614264-3381-4D86-B35F-6F63FD87AB2D}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$4004</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$4006</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8008" uniqueCount="3966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8012" uniqueCount="3968">
   <si>
     <t>AP-REDBLACK-1</t>
   </si>
@@ -11926,6 +11926,12 @@
   </si>
   <si>
     <t>MED-987-WHITE</t>
+  </si>
+  <si>
+    <t>DP-A-727-BLACK</t>
+  </si>
+  <si>
+    <t>SH-A-583-NEWGREEN</t>
   </si>
 </sst>
 </file>
@@ -12277,7 +12283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B05C63DA-F614-4EF5-99B2-E291F7A0171E}">
-  <dimension ref="A1:B4004"/>
+  <dimension ref="A1:B4006"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -44316,6 +44322,22 @@
         <v>582</v>
       </c>
     </row>
+    <row r="4005" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4005" t="s">
+        <v>3966</v>
+      </c>
+      <c r="B4005" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="4006" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4006" t="s">
+        <v>3967</v>
+      </c>
+      <c r="B4006" t="s">
+        <v>2533</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
